--- a/src/data/testdata.xlsx
+++ b/src/data/testdata.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>液体粘度测定</t>
   </si>
@@ -39,6 +39,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>T(</t>
     </r>
     <r>
@@ -62,18 +67,6 @@
   <si>
     <t>L(cm)</t>
   </si>
-  <si>
-    <t>ρ</t>
-  </si>
-  <si>
-    <t>ρ0</t>
-  </si>
-  <si>
-    <t>g</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
 </sst>
 </file>
 
@@ -88,18 +81,13 @@
     <numFmt numFmtId="177" formatCode="0.0_ "/>
     <numFmt numFmtId="178" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -577,159 +565,153 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1257,115 +1239,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7"/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="3" width="9.18181818181818"/>
     <col min="5" max="5" width="9.18181818181818"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
     </row>
-    <row r="3" ht="17" spans="1:9">
-      <c r="A3" s="3" t="s">
+    <row r="3" ht="17" spans="1:4">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>1.005</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="3">
         <v>60.383</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="4">
         <v>19.8</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <v>20.2</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>1.017</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="7"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>1.017</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="7"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="5"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>1.012</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="5"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>1.011</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="7"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B4:B8"/>
     <mergeCell ref="C4:C8"/>
     <mergeCell ref="D4:D8"/>
-    <mergeCell ref="A1:I2"/>
+    <mergeCell ref="A1:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
